--- a/sample_names.xlsx
+++ b/sample_names.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\streamlit sorsolókerék\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\sorsolókerék\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080F6EA4-7EF8-47B6-ABE9-99E4F0D24FC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D97B0E-F820-42A9-96DD-216BEABE600C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8484" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="7" sheetId="3" r:id="rId3"/>
     <sheet name="8" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0" calcOnSave="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -190,10 +190,10 @@
     <t>Lilla</t>
   </si>
   <si>
-    <t>P. Tomi</t>
-  </si>
-  <si>
-    <t>H. Tomi</t>
+    <t>H. Tamás</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> P. Tomi</t>
   </si>
 </sst>
 </file>
@@ -721,7 +721,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
@@ -771,7 +771,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/sample_names.xlsx
+++ b/sample_names.xlsx
@@ -5,25 +5,27 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\sorsolókerék\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\alkalmazásaim\streamlit sorsolókerék\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D97B0E-F820-42A9-96DD-216BEABE600C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E67B3AF-3DA6-4C92-BE0E-166398FCC20A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8484" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5" sheetId="1" r:id="rId1"/>
     <sheet name="6" sheetId="2" r:id="rId2"/>
-    <sheet name="7" sheetId="3" r:id="rId3"/>
-    <sheet name="8" sheetId="4" r:id="rId4"/>
+    <sheet name="3" sheetId="5" r:id="rId3"/>
+    <sheet name="4" sheetId="6" r:id="rId4"/>
+    <sheet name="7" sheetId="3" r:id="rId5"/>
+    <sheet name="8" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
   <si>
     <t>Név</t>
   </si>
@@ -190,10 +192,100 @@
     <t>Lilla</t>
   </si>
   <si>
-    <t>H. Tamás</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> P. Tomi</t>
+    <t>P. Tomi</t>
+  </si>
+  <si>
+    <t>H. Tomi</t>
+  </si>
+  <si>
+    <t>Zolcsi</t>
+  </si>
+  <si>
+    <t>Balázs</t>
+  </si>
+  <si>
+    <t>Ádám</t>
+  </si>
+  <si>
+    <t>Boti</t>
+  </si>
+  <si>
+    <t>Edvárd</t>
+  </si>
+  <si>
+    <t>Eliott</t>
+  </si>
+  <si>
+    <t>Ferike</t>
+  </si>
+  <si>
+    <t>P. Dorina</t>
+  </si>
+  <si>
+    <t>O. Dorina</t>
+  </si>
+  <si>
+    <t>Sz. Hanna</t>
+  </si>
+  <si>
+    <t>S. Hanna</t>
+  </si>
+  <si>
+    <t>Cs. Hanna</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>Kevin</t>
+  </si>
+  <si>
+    <t>Nati</t>
+  </si>
+  <si>
+    <t>Janka</t>
+  </si>
+  <si>
+    <t>Dorina</t>
+  </si>
+  <si>
+    <t>Sanyi</t>
+  </si>
+  <si>
+    <t>Roli</t>
+  </si>
+  <si>
+    <t>Evelin</t>
+  </si>
+  <si>
+    <t>Kristóf</t>
+  </si>
+  <si>
+    <t>Zselyke</t>
+  </si>
+  <si>
+    <t>Dominik</t>
+  </si>
+  <si>
+    <t>Milán</t>
+  </si>
+  <si>
+    <t>Boróka</t>
+  </si>
+  <si>
+    <t>Lili</t>
+  </si>
+  <si>
+    <t>Zoli</t>
+  </si>
+  <si>
+    <t>Erizsike</t>
+  </si>
+  <si>
+    <t>Lejla</t>
+  </si>
+  <si>
+    <t>Iván</t>
   </si>
 </sst>
 </file>
@@ -721,7 +813,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
@@ -771,7 +863,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -780,6 +872,226 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15404671-684A-4203-965E-0B8ACB5E1494}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53819EF9-4B0E-4F16-B1EA-C0CD1981BCE6}">
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -849,7 +1161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40189125-9ED9-443A-82F7-CC51C062B961}">
   <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
